--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N44_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N44_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>67.85086213395084</v>
+        <v>11.02576509676701</v>
       </c>
       <c r="D2" t="n">
-        <v>66.19989540806844</v>
+        <v>10.75748300381112</v>
       </c>
       <c r="E2" t="n">
-        <v>13.41966412735371</v>
+        <v>2.180695420694978</v>
       </c>
       <c r="F2" t="n">
-        <v>13.71534119195046</v>
+        <v>2.228742943691951</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>49.2611875414036</v>
+        <v>8.004942975478086</v>
       </c>
       <c r="D3" t="n">
-        <v>48.44427879308929</v>
+        <v>7.872195303877009</v>
       </c>
       <c r="E3" t="n">
-        <v>13.41966412735371</v>
+        <v>2.180695420694978</v>
       </c>
       <c r="F3" t="n">
-        <v>13.71534119195046</v>
+        <v>2.228742943691951</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>45.30463119585755</v>
+        <v>7.362002569326853</v>
       </c>
       <c r="D4" t="n">
-        <v>43.68757022023757</v>
+        <v>7.099230160788605</v>
       </c>
       <c r="E4" t="n">
-        <v>13.41966412735371</v>
+        <v>2.180695420694978</v>
       </c>
       <c r="F4" t="n">
-        <v>13.71534119195046</v>
+        <v>2.228742943691951</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>22.23177307978894</v>
+        <v>3.612663125465702</v>
       </c>
       <c r="D5" t="n">
-        <v>20.71006934003299</v>
+        <v>3.365386267755362</v>
       </c>
       <c r="E5" t="n">
-        <v>13.41966412735371</v>
+        <v>2.180695420694978</v>
       </c>
       <c r="F5" t="n">
-        <v>13.71534119195046</v>
+        <v>2.228742943691951</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>47.83105856713678</v>
+        <v>7.772547017159726</v>
       </c>
       <c r="D6" t="n">
-        <v>48.97392385399069</v>
+        <v>7.958262626273488</v>
       </c>
       <c r="E6" t="n">
-        <v>13.41966412735371</v>
+        <v>2.180695420694978</v>
       </c>
       <c r="F6" t="n">
-        <v>13.71534119195046</v>
+        <v>2.228742943691951</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>56.32542310722723</v>
+        <v>9.152881254924425</v>
       </c>
       <c r="D7" t="n">
-        <v>57.62984945604835</v>
+        <v>9.364850536607857</v>
       </c>
       <c r="E7" t="n">
-        <v>13.41966412735371</v>
+        <v>2.180695420694978</v>
       </c>
       <c r="F7" t="n">
-        <v>13.71534119195046</v>
+        <v>2.228742943691951</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>52.83986562653986</v>
+        <v>8.586478164312728</v>
       </c>
       <c r="D8" t="n">
-        <v>52.45633809309223</v>
+        <v>8.524154940127488</v>
       </c>
       <c r="E8" t="n">
-        <v>13.41966412735371</v>
+        <v>2.180695420694978</v>
       </c>
       <c r="F8" t="n">
-        <v>13.71534119195046</v>
+        <v>2.228742943691951</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>47.25041998975188</v>
+        <v>7.67819324833468</v>
       </c>
       <c r="D9" t="n">
-        <v>47.21983016785133</v>
+        <v>7.673222402275841</v>
       </c>
       <c r="E9" t="n">
-        <v>13.41966412735371</v>
+        <v>2.180695420694978</v>
       </c>
       <c r="F9" t="n">
-        <v>13.71534119195046</v>
+        <v>2.228742943691951</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>50.64664039639076</v>
+        <v>8.230079064413498</v>
       </c>
       <c r="D10" t="n">
-        <v>51.86057888496484</v>
+        <v>8.427344068806788</v>
       </c>
       <c r="E10" t="n">
-        <v>13.41966412735371</v>
+        <v>2.180695420694978</v>
       </c>
       <c r="F10" t="n">
-        <v>13.71534119195046</v>
+        <v>2.228742943691951</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>55.18746763841454</v>
+        <v>8.967963491242363</v>
       </c>
       <c r="D11" t="n">
-        <v>56.69121838432556</v>
+        <v>9.212322987452904</v>
       </c>
       <c r="E11" t="n">
-        <v>13.41966412735371</v>
+        <v>2.180695420694978</v>
       </c>
       <c r="F11" t="n">
-        <v>13.71534119195046</v>
+        <v>2.228742943691951</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>53.86255774641293</v>
+        <v>8.7526656337921</v>
       </c>
       <c r="D12" t="n">
-        <v>55.22533987497546</v>
+        <v>8.974117729683513</v>
       </c>
       <c r="E12" t="n">
-        <v>13.41966412735371</v>
+        <v>2.180695420694978</v>
       </c>
       <c r="F12" t="n">
-        <v>13.71534119195046</v>
+        <v>2.228742943691951</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>25.59065809683301</v>
+        <v>4.158481940735363</v>
       </c>
       <c r="D13" t="n">
-        <v>25.09232691718814</v>
+        <v>4.077503124043074</v>
       </c>
       <c r="E13" t="n">
-        <v>13.41966412735371</v>
+        <v>2.180695420694978</v>
       </c>
       <c r="F13" t="n">
-        <v>13.71534119195046</v>
+        <v>2.228742943691951</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>38.10106170460128</v>
+        <v>6.191422526997708</v>
       </c>
       <c r="D14" t="n">
-        <v>38.18814684166739</v>
+        <v>6.205573861770951</v>
       </c>
       <c r="E14" t="n">
-        <v>13.41966412735371</v>
+        <v>2.180695420694978</v>
       </c>
       <c r="F14" t="n">
-        <v>13.71534119195046</v>
+        <v>2.228742943691951</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0706030031978</v>
+        <v>3.261472988019642</v>
       </c>
       <c r="D15" t="n">
-        <v>20.21791152332971</v>
+        <v>3.285410622541079</v>
       </c>
       <c r="E15" t="n">
-        <v>13.41966412735371</v>
+        <v>2.180695420694978</v>
       </c>
       <c r="F15" t="n">
-        <v>13.71534119195046</v>
+        <v>2.228742943691951</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
